--- a/TestCase game.xlsx
+++ b/TestCase game.xlsx
@@ -17,9 +17,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>TC_Practical-001</t>
   </si>
   <si>
     <t>Test Case Desc</t>
@@ -198,6 +195,9 @@
   </si>
   <si>
     <t>Test the Functionality of user interface on Tic Tac Toe game.</t>
+  </si>
+  <si>
+    <t>TC_Practical-005</t>
   </si>
 </sst>
 </file>
@@ -600,10 +600,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -613,15 +609,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -631,17 +618,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -658,17 +636,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -678,18 +651,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -697,20 +664,53 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -985,24 +985,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>2</v>
+      <c r="E1" s="5"/>
+      <c r="F1" s="42" t="s">
+        <v>59</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="10"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -1020,27 +1020,27 @@
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="G2" s="28"/>
+      <c r="H2" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16" t="s">
+      <c r="I2" s="28"/>
+      <c r="J2" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="18" t="s">
-        <v>20</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1059,22 +1059,22 @@
       <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="20"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="10"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1092,16 +1092,16 @@
       <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="23"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="13"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1119,23 +1119,23 @@
       <c r="Y4" s="1"/>
     </row>
     <row r="5" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
       <c r="J5" s="29"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1154,21 +1154,21 @@
       <c r="Y5" s="1"/>
     </row>
     <row r="6" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30">
+      <c r="A6" s="17">
         <v>1</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>59</v>
+      <c r="B6" s="26" t="s">
+        <v>58</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="31">
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="18">
         <v>1</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
       <c r="J6" s="29"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1187,19 +1187,19 @@
       <c r="Y6" s="1"/>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="30">
+      <c r="A7" s="17">
         <v>2</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="31">
+      <c r="B7" s="26"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="18">
         <v>2</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
       <c r="J7" s="29"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1218,19 +1218,19 @@
       <c r="Y7" s="1"/>
     </row>
     <row r="8" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="30">
+      <c r="A8" s="17">
         <v>3</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="31">
+      <c r="B8" s="26"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="18">
         <v>3</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
       <c r="J8" s="29"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1249,20 +1249,20 @@
       <c r="Y8" s="1"/>
     </row>
     <row r="9" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="32">
+      <c r="A9" s="19">
         <v>4</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="37">
+      <c r="B9" s="30"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="21">
         <v>4</v>
       </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="38"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="33"/>
       <c r="K9" s="2"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1280,16 +1280,16 @@
       <c r="Y9" s="1"/>
     </row>
     <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="39"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1307,18 +1307,18 @@
       <c r="Y10" s="1"/>
     </row>
     <row r="11" spans="1:25" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="40" t="s">
-        <v>12</v>
+      <c r="A11" s="23" t="s">
+        <v>11</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1336,16 +1336,16 @@
       <c r="Y11" s="1"/>
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1363,16 +1363,16 @@
       <c r="Y12" s="1"/>
     </row>
     <row r="13" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1390,26 +1390,26 @@
       <c r="Y13" s="1"/>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="C14" s="38"/>
+      <c r="D14" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="46" t="s">
+      <c r="E14" s="38"/>
+      <c r="F14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="46" t="s">
+      <c r="G14" s="39"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="10"/>
+      <c r="J14" s="40"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1427,21 +1427,21 @@
       <c r="Y14" s="1"/>
     </row>
     <row r="15" spans="1:25" ht="163.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="30">
+      <c r="A15" s="17">
         <v>1</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="16"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="26"/>
       <c r="J15" s="29"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1460,21 +1460,21 @@
       <c r="Y15" s="1"/>
     </row>
     <row r="16" spans="1:25" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30">
+      <c r="A16" s="17">
         <v>2</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="16"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="26"/>
       <c r="J16" s="29"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1493,21 +1493,21 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="30">
+      <c r="A17" s="17">
         <v>3</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="16"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="26"/>
       <c r="J17" s="29"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1526,21 +1526,21 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="30">
+      <c r="A18" s="17">
         <v>4</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="16"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="26"/>
       <c r="J18" s="29"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1559,21 +1559,21 @@
       <c r="Y18" s="1"/>
     </row>
     <row r="19" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="30">
+      <c r="A19" s="17">
         <v>5</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="16"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="26"/>
       <c r="J19" s="29"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1592,21 +1592,21 @@
       <c r="Y19" s="1"/>
     </row>
     <row r="20" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="30">
+      <c r="A20" s="17">
         <v>6</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="16"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="26"/>
       <c r="J20" s="29"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1625,21 +1625,21 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="30">
+      <c r="A21" s="17">
         <v>7</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="28"/>
+      <c r="D21" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="16"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="26"/>
       <c r="J21" s="29"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1658,21 +1658,21 @@
       <c r="Y21" s="1"/>
     </row>
     <row r="22" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="30">
+      <c r="A22" s="17">
         <v>8</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="16" t="s">
+      <c r="B22" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="16"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="26"/>
       <c r="J22" s="29"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1691,21 +1691,21 @@
       <c r="Y22" s="1"/>
     </row>
     <row r="23" spans="1:25" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="30">
+      <c r="A23" s="17">
         <v>9</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>36</v>
+      <c r="B23" s="26" t="s">
+        <v>35</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="16" t="s">
-        <v>34</v>
+      <c r="C23" s="28"/>
+      <c r="D23" s="26" t="s">
+        <v>33</v>
       </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="16"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="26"/>
       <c r="J23" s="29"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1724,21 +1724,21 @@
       <c r="Y23" s="1"/>
     </row>
     <row r="24" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="30">
+      <c r="A24" s="17">
         <v>10</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="16"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="26"/>
       <c r="J24" s="29"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1757,21 +1757,21 @@
       <c r="Y24" s="1"/>
     </row>
     <row r="25" spans="1:25" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="30">
+      <c r="A25" s="17">
         <v>11</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="16"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="26"/>
       <c r="J25" s="29"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1790,21 +1790,21 @@
       <c r="Y25" s="1"/>
     </row>
     <row r="26" spans="1:25" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="30">
+      <c r="A26" s="17">
         <v>12</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="16"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="26"/>
       <c r="J26" s="29"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1823,21 +1823,21 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="30">
+      <c r="A27" s="17">
         <v>13</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="16"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="26"/>
       <c r="J27" s="29"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1856,21 +1856,21 @@
       <c r="Y27" s="1"/>
     </row>
     <row r="28" spans="1:25" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="30">
+      <c r="A28" s="17">
         <v>14</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="28"/>
+      <c r="D28" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="16"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="26"/>
       <c r="J28" s="29"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1889,21 +1889,21 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="29" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="30">
+      <c r="A29" s="17">
         <v>15</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="28"/>
+      <c r="D29" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="16"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="26"/>
       <c r="J29" s="29"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1922,21 +1922,21 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="30" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="30">
+      <c r="A30" s="17">
         <v>16</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="16"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="26"/>
       <c r="J30" s="29"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1955,21 +1955,21 @@
       <c r="Y30" s="1"/>
     </row>
     <row r="31" spans="1:25" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="30">
+      <c r="A31" s="17">
         <v>17</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="12"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="16"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="26"/>
       <c r="J31" s="29"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1988,21 +1988,21 @@
       <c r="Y31" s="1"/>
     </row>
     <row r="32" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="30">
+      <c r="A32" s="17">
         <v>18</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="28"/>
+      <c r="D32" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="16"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="26"/>
       <c r="J32" s="29"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -2021,21 +2021,21 @@
       <c r="Y32" s="1"/>
     </row>
     <row r="33" spans="1:25" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="30">
+      <c r="A33" s="17">
         <v>19</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="16"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="26"/>
       <c r="J33" s="29"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2054,22 +2054,22 @@
       <c r="Y33" s="1"/>
     </row>
     <row r="34" spans="1:25" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="32">
+      <c r="A34" s="19">
         <v>20</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="31"/>
+      <c r="D34" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="E34" s="35"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="38"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="33"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2087,16 +2087,16 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="43"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -28008,6 +28008,86 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="B24:C24"/>
@@ -28032,86 +28112,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
